--- a/data/trans_camb/IP13-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP13-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,08</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,08</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,15</t>
+          <t>-4,31; 5,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 5,53</t>
+          <t>-7,53; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 6,58</t>
+          <t>-6,9; 5,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,19</t>
+          <t>-3,63; 6,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,56</t>
+          <t>-5,01; 5,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,57</t>
+          <t>-5,88; 6,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,62</t>
+          <t>-2,68; 5,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 2,07</t>
+          <t>-4,93; 2,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,32</t>
+          <t>-5,12; 3,84</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,01%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-43,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-19,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>21,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,96%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-43,38%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-25,33%</t>
+          <t>-3,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-13,69%</t>
+          <t>-11,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 190,36</t>
+          <t>-46,62; 135,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 137,66</t>
+          <t>-81,08; 32,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,16; 154,99</t>
+          <t>-76,78; 131,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,38; 130,35</t>
+          <t>-38,32; 164,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,88; 52,66</t>
+          <t>-50,3; 138,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,03; 109,65</t>
+          <t>-65,21; 143,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 83,93</t>
+          <t>-29,42; 101,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,94; 39,08</t>
+          <t>-53,74; 41,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 62,71</t>
+          <t>-59,67; 74,55</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,39</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,61</t>
+          <t>-1,19; 5,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,51</t>
+          <t>-2,94; 2,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,01</t>
+          <t>-0,36; 7,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,99</t>
+          <t>-2,35; 3,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,76</t>
+          <t>-0,85; 5,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,2</t>
+          <t>-2,06; 5,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,93</t>
+          <t>-0,84; 3,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,05</t>
+          <t>-1,26; 3,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,99</t>
+          <t>-0,12; 5,11</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>54,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,91%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 120,23</t>
+          <t>-23,3; 180,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 180,31</t>
+          <t>-52,54; 82,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 167,94</t>
+          <t>-8,13; 202,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 179,28</t>
+          <t>-43,98; 140,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 93,14</t>
+          <t>-16,82; 177,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 219,5</t>
+          <t>-39,13; 170,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 115,51</t>
+          <t>-17,1; 101,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 83,9</t>
+          <t>-22,11; 88,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 137,29</t>
+          <t>-4,94; 141,92</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,39</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,07</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,57</t>
+          <t>-8,14; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,32</t>
+          <t>-5,8; 2,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,44</t>
+          <t>-3,34; 6,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 0,39</t>
+          <t>-2,78; 4,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 2,75</t>
+          <t>-3,03; 4,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,79</t>
+          <t>-0,75; 7,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,16</t>
+          <t>-4,13; 1,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,59</t>
+          <t>-3,06; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,14</t>
+          <t>-0,93; 5,63</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-57,25%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-20,89%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>33,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>36,52%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>108,03%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-57,25%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-20,89%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>106,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 448,88</t>
+          <t>-87,77; 12,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,05; 459,31</t>
+          <t>-64,76; 71,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 732,98</t>
+          <t>-40,41; 153,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,66; 29,3</t>
+          <t>-58,4; 377,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 67,26</t>
+          <t>-57,04; 344,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 133,41</t>
+          <t>-27,33; 477,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 39,2</t>
+          <t>-64,74; 44,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 80,2</t>
+          <t>-46,1; 81,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 146,85</t>
+          <t>-22,23; 170,24</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,08</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,93</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,68</t>
+          <t>-0,09; 7,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,3</t>
+          <t>-2,37; 3,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 4,08</t>
+          <t>-1,34; 5,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,74</t>
+          <t>-2,64; 4,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,39</t>
+          <t>-4,05; 2,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,8</t>
+          <t>-1,73; 5,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,58</t>
+          <t>-0,49; 4,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,38</t>
+          <t>-2,28; 2,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,38</t>
+          <t>-0,47; 4,0</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>95,78%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>62,23%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>25,81%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-22,34%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20,55%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,63; 206,65</t>
+          <t>-9,41; 384,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,84; 103,28</t>
+          <t>-55,9; 236,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 164,46</t>
+          <t>-30,47; 299,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 369,85</t>
+          <t>-49,09; 168,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 236,41</t>
+          <t>-72,42; 98,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 283,19</t>
+          <t>-32,28; 208,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 184,96</t>
+          <t>-9,8; 179,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 95,44</t>
+          <t>-51,21; 90,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 122,49</t>
+          <t>-11,43; 159,18</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,8</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,78</t>
+          <t>-0,66; 3,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,64</t>
+          <t>-2,34; 1,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,06</t>
+          <t>-0,35; 3,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,16</t>
+          <t>-0,95; 3,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,15</t>
+          <t>-1,0; 2,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,45</t>
+          <t>-0,47; 3,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,49</t>
+          <t>-0,28; 2,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,37</t>
+          <t>-1,15; 1,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,71</t>
+          <t>0,05; 2,94</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>17,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-11,68%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 78,53</t>
+          <t>-11,32; 73,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 74,82</t>
+          <t>-38,8; 30,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 84,96</t>
+          <t>-6,34; 88,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 75,61</t>
+          <t>-17,93; 85,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 27,4</t>
+          <t>-18,98; 69,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 84,85</t>
+          <t>-9,31; 102,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 59,6</t>
+          <t>-5,8; 57,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 33,84</t>
+          <t>-21,97; 34,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 65,8</t>
+          <t>0,28; 70,19</t>
         </is>
       </c>
     </row>
